--- a/LAB_1/college_data.xlsx
+++ b/LAB_1/college_data.xlsx
@@ -420,7 +420,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Rool_No</t>
+          <t>Roll_No</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>200</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5">
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>500</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
